--- a/data/cheffelo_trends_monthly.xlsx
+++ b/data/cheffelo_trends_monthly.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,886 +461,1481 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>44561</v>
+        <v>43496</v>
       </c>
       <c r="B2" t="n">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D2" t="n">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="E2" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>44592</v>
+        <v>43524</v>
       </c>
       <c r="B3" t="n">
-        <v>76.2</v>
+        <v>52</v>
       </c>
       <c r="C3" t="n">
-        <v>50.8</v>
+        <v>58</v>
       </c>
       <c r="D3" t="n">
-        <v>86.8</v>
+        <v>51</v>
       </c>
       <c r="E3" t="n">
-        <v>80.8</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>44620</v>
+        <v>43555</v>
       </c>
       <c r="B4" t="n">
-        <v>45.75</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>37.25</v>
+        <v>45</v>
       </c>
       <c r="D4" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E4" t="n">
-        <v>38.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>44651</v>
+        <v>43585</v>
       </c>
       <c r="B5" t="n">
-        <v>54.5</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>45.75</v>
+        <v>45</v>
       </c>
       <c r="D5" t="n">
-        <v>43.5</v>
+        <v>45</v>
       </c>
       <c r="E5" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>44681</v>
+        <v>43616</v>
       </c>
       <c r="B6" t="n">
-        <v>44.25</v>
+        <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>35.75</v>
+        <v>33</v>
       </c>
       <c r="E6" t="n">
-        <v>17.75</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>44712</v>
+        <v>43646</v>
       </c>
       <c r="B7" t="n">
-        <v>39.8</v>
+        <v>32</v>
       </c>
       <c r="C7" t="n">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="D7" t="n">
-        <v>28.6</v>
+        <v>31</v>
       </c>
       <c r="E7" t="n">
-        <v>16.2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>44742</v>
+        <v>43677</v>
       </c>
       <c r="B8" t="n">
-        <v>32.25</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>22.25</v>
+        <v>31</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>44773</v>
+        <v>43708</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="D9" t="n">
-        <v>21.2</v>
+        <v>64</v>
       </c>
       <c r="E9" t="n">
-        <v>5.4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>44804</v>
+        <v>43738</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75</v>
+        <v>75</v>
       </c>
       <c r="D10" t="n">
-        <v>53.25</v>
+        <v>59</v>
       </c>
       <c r="E10" t="n">
-        <v>26.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>44834</v>
+        <v>43769</v>
       </c>
       <c r="B11" t="n">
-        <v>52.5</v>
+        <v>60</v>
       </c>
       <c r="C11" t="n">
-        <v>32.25</v>
+        <v>42</v>
       </c>
       <c r="D11" t="n">
-        <v>45.5</v>
+        <v>53</v>
       </c>
       <c r="E11" t="n">
-        <v>30.75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>44865</v>
+        <v>43799</v>
       </c>
       <c r="B12" t="n">
+        <v>49</v>
+      </c>
+      <c r="C12" t="n">
+        <v>38</v>
+      </c>
+      <c r="D12" t="n">
         <v>45</v>
       </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>38.4</v>
-      </c>
       <c r="E12" t="n">
-        <v>5.6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>44895</v>
+        <v>43830</v>
       </c>
       <c r="B13" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D13" t="n">
-        <v>28.75</v>
+        <v>32</v>
       </c>
       <c r="E13" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>44926</v>
+        <v>43861</v>
       </c>
       <c r="B14" t="n">
-        <v>34.5</v>
+        <v>94</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>22.5</v>
+        <v>74</v>
       </c>
       <c r="E14" t="n">
-        <v>5.75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>44957</v>
+        <v>43890</v>
       </c>
       <c r="B15" t="n">
-        <v>85.40000000000001</v>
+        <v>54</v>
       </c>
       <c r="C15" t="n">
-        <v>16.6</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E15" t="n">
-        <v>40.4</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>44985</v>
+        <v>43921</v>
       </c>
       <c r="B16" t="n">
-        <v>47.25</v>
+        <v>56</v>
       </c>
       <c r="C16" t="n">
-        <v>18.75</v>
+        <v>83</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="E16" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45016</v>
+        <v>43951</v>
       </c>
       <c r="B17" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="D17" t="n">
-        <v>27.25</v>
+        <v>63</v>
       </c>
       <c r="E17" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45046</v>
+        <v>43982</v>
       </c>
       <c r="B18" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C18" t="n">
-        <v>10.8</v>
+        <v>69</v>
       </c>
       <c r="D18" t="n">
-        <v>20.8</v>
+        <v>46</v>
       </c>
       <c r="E18" t="n">
-        <v>22.8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45077</v>
+        <v>44012</v>
       </c>
       <c r="B19" t="n">
-        <v>25.25</v>
+        <v>36</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="D19" t="n">
-        <v>13.5</v>
+        <v>37</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45107</v>
+        <v>44043</v>
       </c>
       <c r="B20" t="n">
-        <v>20.5</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>21.25</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
-        <v>18.75</v>
+        <v>29</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45138</v>
+        <v>44074</v>
       </c>
       <c r="B21" t="n">
-        <v>26.2</v>
+        <v>81</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="D21" t="n">
-        <v>17.8</v>
+        <v>80</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45169</v>
+        <v>44104</v>
       </c>
       <c r="B22" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C22" t="n">
-        <v>14.75</v>
+        <v>100</v>
       </c>
       <c r="D22" t="n">
-        <v>38.5</v>
+        <v>86</v>
       </c>
       <c r="E22" t="n">
-        <v>36.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45199</v>
+        <v>44135</v>
       </c>
       <c r="B23" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D23" t="n">
-        <v>32.75</v>
+        <v>64</v>
       </c>
       <c r="E23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45230</v>
+        <v>44165</v>
       </c>
       <c r="B24" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="C24" t="n">
-        <v>18.6</v>
+        <v>84</v>
       </c>
       <c r="D24" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="E24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45260</v>
+        <v>44196</v>
       </c>
       <c r="B25" t="n">
-        <v>32.75</v>
+        <v>54</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="D25" t="n">
-        <v>22.75</v>
+        <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45291</v>
+        <v>44227</v>
       </c>
       <c r="B26" t="n">
-        <v>34.4</v>
+        <v>100</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="D26" t="n">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="E26" t="n">
-        <v>45.4</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45322</v>
+        <v>44255</v>
       </c>
       <c r="B27" t="n">
-        <v>50.75</v>
+        <v>76</v>
       </c>
       <c r="C27" t="n">
-        <v>13.25</v>
+        <v>89</v>
       </c>
       <c r="D27" t="n">
-        <v>39.25</v>
+        <v>77</v>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45351</v>
+        <v>44286</v>
       </c>
       <c r="B28" t="n">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="D28" t="n">
-        <v>25.5</v>
+        <v>54</v>
       </c>
       <c r="E28" t="n">
-        <v>29.25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45382</v>
+        <v>44316</v>
       </c>
       <c r="B29" t="n">
-        <v>29.8</v>
+        <v>63</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D29" t="n">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="E29" t="n">
-        <v>19.6</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45412</v>
+        <v>44347</v>
       </c>
       <c r="B30" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D30" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E30" t="n">
-        <v>11.25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45443</v>
+        <v>44377</v>
       </c>
       <c r="B31" t="n">
-        <v>22.25</v>
+        <v>27</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D31" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45473</v>
+        <v>44408</v>
       </c>
       <c r="B32" t="n">
-        <v>17.4</v>
+        <v>20</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D32" t="n">
-        <v>2.6</v>
+        <v>26</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45504</v>
+        <v>44439</v>
       </c>
       <c r="B33" t="n">
-        <v>16.75</v>
+        <v>47</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45535</v>
+        <v>44469</v>
       </c>
       <c r="B34" t="n">
-        <v>44.25</v>
+        <v>48</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D34" t="n">
-        <v>35.75</v>
+        <v>62</v>
       </c>
       <c r="E34" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45565</v>
+        <v>44500</v>
       </c>
       <c r="B35" t="n">
-        <v>33.6</v>
+        <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="D35" t="n">
-        <v>24.6</v>
+        <v>48</v>
       </c>
       <c r="E35" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45596</v>
+        <v>44530</v>
       </c>
       <c r="B36" t="n">
-        <v>29.25</v>
+        <v>37</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D36" t="n">
-        <v>26.25</v>
+        <v>38</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45626</v>
+        <v>44561</v>
       </c>
       <c r="B37" t="n">
-        <v>26.5</v>
+        <v>29</v>
       </c>
       <c r="C37" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D37" t="n">
-        <v>20.25</v>
+        <v>36</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45657</v>
+        <v>44592</v>
       </c>
       <c r="B38" t="n">
-        <v>23.2</v>
+        <v>61</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="D38" t="n">
-        <v>16.8</v>
+        <v>96</v>
       </c>
       <c r="E38" t="n">
-        <v>16.6</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45688</v>
+        <v>44620</v>
       </c>
       <c r="B39" t="n">
-        <v>38.5</v>
+        <v>40</v>
       </c>
       <c r="C39" t="n">
-        <v>39.75</v>
+        <v>65</v>
       </c>
       <c r="D39" t="n">
-        <v>36.5</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>41.25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45716</v>
+        <v>44651</v>
       </c>
       <c r="B40" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C40" t="n">
-        <v>15.75</v>
+        <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>27.75</v>
+        <v>46</v>
       </c>
       <c r="E40" t="n">
-        <v>12.75</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45747</v>
+        <v>44681</v>
       </c>
       <c r="B41" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>29.4</v>
+        <v>36</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45777</v>
+        <v>44712</v>
       </c>
       <c r="B42" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D42" t="n">
-        <v>14.5</v>
+        <v>33</v>
       </c>
       <c r="E42" t="n">
-        <v>9.25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45808</v>
+        <v>44742</v>
       </c>
       <c r="B43" t="n">
-        <v>21.25</v>
+        <v>25</v>
       </c>
       <c r="C43" t="n">
-        <v>19.5</v>
+        <v>33</v>
       </c>
       <c r="D43" t="n">
-        <v>12.25</v>
+        <v>25</v>
       </c>
       <c r="E43" t="n">
-        <v>7.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45838</v>
+        <v>44773</v>
       </c>
       <c r="B44" t="n">
-        <v>16.2</v>
+        <v>20</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D44" t="n">
-        <v>4.8</v>
+        <v>21</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45869</v>
+        <v>44804</v>
       </c>
       <c r="B45" t="n">
-        <v>16.25</v>
+        <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D45" t="n">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45900</v>
+        <v>44834</v>
       </c>
       <c r="B46" t="n">
-        <v>46.4</v>
+        <v>41</v>
       </c>
       <c r="C46" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="D46" t="n">
-        <v>42.2</v>
+        <v>47</v>
       </c>
       <c r="E46" t="n">
-        <v>20.8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45930</v>
+        <v>44865</v>
       </c>
       <c r="B47" t="n">
         <v>38</v>
       </c>
       <c r="C47" t="n">
-        <v>24.75</v>
+        <v>63</v>
       </c>
       <c r="D47" t="n">
-        <v>28.25</v>
+        <v>41</v>
       </c>
       <c r="E47" t="n">
-        <v>6.75</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45961</v>
+        <v>44895</v>
       </c>
       <c r="B48" t="n">
-        <v>34.25</v>
+        <v>31</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D48" t="n">
-        <v>21.75</v>
+        <v>33</v>
       </c>
       <c r="E48" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45991</v>
+        <v>44926</v>
       </c>
       <c r="B49" t="n">
-        <v>26.8</v>
+        <v>28</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D49" t="n">
-        <v>16.4</v>
+        <v>26</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46022</v>
+        <v>44957</v>
       </c>
       <c r="B50" t="n">
-        <v>28.5</v>
+        <v>72</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46053</v>
+        <v>44985</v>
       </c>
       <c r="B51" t="n">
-        <v>56.5</v>
+        <v>39</v>
       </c>
       <c r="C51" t="n">
-        <v>16.25</v>
+        <v>57</v>
       </c>
       <c r="D51" t="n">
-        <v>24.25</v>
+        <v>45</v>
       </c>
       <c r="E51" t="n">
-        <v>42.75</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46081</v>
+        <v>45016</v>
       </c>
       <c r="B52" t="n">
-        <v>36.25</v>
+        <v>35</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D52" t="n">
-        <v>21.75</v>
+        <v>30</v>
       </c>
       <c r="E52" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
+        <v>45046</v>
+      </c>
+      <c r="B53" t="n">
+        <v>27</v>
+      </c>
+      <c r="C53" t="n">
+        <v>37</v>
+      </c>
+      <c r="D53" t="n">
+        <v>25</v>
+      </c>
+      <c r="E53" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45077</v>
+      </c>
+      <c r="B54" t="n">
+        <v>22</v>
+      </c>
+      <c r="C54" t="n">
+        <v>24</v>
+      </c>
+      <c r="D54" t="n">
+        <v>21</v>
+      </c>
+      <c r="E54" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45107</v>
+      </c>
+      <c r="B55" t="n">
+        <v>17</v>
+      </c>
+      <c r="C55" t="n">
+        <v>27</v>
+      </c>
+      <c r="D55" t="n">
+        <v>21</v>
+      </c>
+      <c r="E55" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>45138</v>
+      </c>
+      <c r="B56" t="n">
+        <v>18</v>
+      </c>
+      <c r="C56" t="n">
+        <v>31</v>
+      </c>
+      <c r="D56" t="n">
+        <v>20</v>
+      </c>
+      <c r="E56" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>45169</v>
+      </c>
+      <c r="B57" t="n">
+        <v>43</v>
+      </c>
+      <c r="C57" t="n">
+        <v>43</v>
+      </c>
+      <c r="D57" t="n">
+        <v>39</v>
+      </c>
+      <c r="E57" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45199</v>
+      </c>
+      <c r="B58" t="n">
+        <v>33</v>
+      </c>
+      <c r="C58" t="n">
+        <v>38</v>
+      </c>
+      <c r="D58" t="n">
+        <v>34</v>
+      </c>
+      <c r="E58" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45230</v>
+      </c>
+      <c r="B59" t="n">
+        <v>32</v>
+      </c>
+      <c r="C59" t="n">
+        <v>40</v>
+      </c>
+      <c r="D59" t="n">
+        <v>30</v>
+      </c>
+      <c r="E59" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>45260</v>
+      </c>
+      <c r="B60" t="n">
+        <v>26</v>
+      </c>
+      <c r="C60" t="n">
+        <v>33</v>
+      </c>
+      <c r="D60" t="n">
+        <v>25</v>
+      </c>
+      <c r="E60" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>45291</v>
+      </c>
+      <c r="B61" t="n">
+        <v>22</v>
+      </c>
+      <c r="C61" t="n">
+        <v>22</v>
+      </c>
+      <c r="D61" t="n">
+        <v>17</v>
+      </c>
+      <c r="E61" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>45322</v>
+      </c>
+      <c r="B62" t="n">
+        <v>44</v>
+      </c>
+      <c r="C62" t="n">
+        <v>27</v>
+      </c>
+      <c r="D62" t="n">
+        <v>47</v>
+      </c>
+      <c r="E62" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>45351</v>
+      </c>
+      <c r="B63" t="n">
+        <v>31</v>
+      </c>
+      <c r="C63" t="n">
+        <v>41</v>
+      </c>
+      <c r="D63" t="n">
+        <v>31</v>
+      </c>
+      <c r="E63" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B64" t="n">
+        <v>23</v>
+      </c>
+      <c r="C64" t="n">
+        <v>21</v>
+      </c>
+      <c r="D64" t="n">
+        <v>27</v>
+      </c>
+      <c r="E64" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>45412</v>
+      </c>
+      <c r="B65" t="n">
+        <v>26</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>23</v>
+      </c>
+      <c r="E65" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45443</v>
+      </c>
+      <c r="B66" t="n">
+        <v>18</v>
+      </c>
+      <c r="C66" t="n">
+        <v>15</v>
+      </c>
+      <c r="D66" t="n">
+        <v>17</v>
+      </c>
+      <c r="E66" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45473</v>
+      </c>
+      <c r="B67" t="n">
+        <v>14</v>
+      </c>
+      <c r="C67" t="n">
+        <v>21</v>
+      </c>
+      <c r="D67" t="n">
+        <v>11</v>
+      </c>
+      <c r="E67" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45504</v>
+      </c>
+      <c r="B68" t="n">
+        <v>15</v>
+      </c>
+      <c r="C68" t="n">
+        <v>16</v>
+      </c>
+      <c r="D68" t="n">
+        <v>17</v>
+      </c>
+      <c r="E68" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45535</v>
+      </c>
+      <c r="B69" t="n">
+        <v>35</v>
+      </c>
+      <c r="C69" t="n">
+        <v>43</v>
+      </c>
+      <c r="D69" t="n">
+        <v>35</v>
+      </c>
+      <c r="E69" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45565</v>
+      </c>
+      <c r="B70" t="n">
+        <v>29</v>
+      </c>
+      <c r="C70" t="n">
+        <v>44</v>
+      </c>
+      <c r="D70" t="n">
+        <v>29</v>
+      </c>
+      <c r="E70" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45596</v>
+      </c>
+      <c r="B71" t="n">
+        <v>25</v>
+      </c>
+      <c r="C71" t="n">
+        <v>41</v>
+      </c>
+      <c r="D71" t="n">
+        <v>27</v>
+      </c>
+      <c r="E71" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45626</v>
+      </c>
+      <c r="B72" t="n">
+        <v>21</v>
+      </c>
+      <c r="C72" t="n">
+        <v>42</v>
+      </c>
+      <c r="D72" t="n">
+        <v>20</v>
+      </c>
+      <c r="E72" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45657</v>
+      </c>
+      <c r="B73" t="n">
+        <v>18</v>
+      </c>
+      <c r="C73" t="n">
+        <v>22</v>
+      </c>
+      <c r="D73" t="n">
+        <v>16</v>
+      </c>
+      <c r="E73" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B74" t="n">
+        <v>32</v>
+      </c>
+      <c r="C74" t="n">
+        <v>60</v>
+      </c>
+      <c r="D74" t="n">
+        <v>39</v>
+      </c>
+      <c r="E74" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B75" t="n">
+        <v>28</v>
+      </c>
+      <c r="C75" t="n">
+        <v>52</v>
+      </c>
+      <c r="D75" t="n">
+        <v>30</v>
+      </c>
+      <c r="E75" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45747</v>
+      </c>
+      <c r="B76" t="n">
+        <v>24</v>
+      </c>
+      <c r="C76" t="n">
+        <v>24</v>
+      </c>
+      <c r="D76" t="n">
+        <v>30</v>
+      </c>
+      <c r="E76" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B77" t="n">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>40</v>
+      </c>
+      <c r="D77" t="n">
+        <v>22</v>
+      </c>
+      <c r="E77" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B78" t="n">
+        <v>17</v>
+      </c>
+      <c r="C78" t="n">
+        <v>27</v>
+      </c>
+      <c r="D78" t="n">
+        <v>15</v>
+      </c>
+      <c r="E78" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B79" t="n">
+        <v>14</v>
+      </c>
+      <c r="C79" t="n">
+        <v>30</v>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B80" t="n">
+        <v>14</v>
+      </c>
+      <c r="C80" t="n">
+        <v>28</v>
+      </c>
+      <c r="D80" t="n">
+        <v>15</v>
+      </c>
+      <c r="E80" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B81" t="n">
+        <v>39</v>
+      </c>
+      <c r="C81" t="n">
+        <v>68</v>
+      </c>
+      <c r="D81" t="n">
+        <v>42</v>
+      </c>
+      <c r="E81" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B82" t="n">
+        <v>30</v>
+      </c>
+      <c r="C82" t="n">
+        <v>43</v>
+      </c>
+      <c r="D82" t="n">
+        <v>34</v>
+      </c>
+      <c r="E82" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B83" t="n">
+        <v>27</v>
+      </c>
+      <c r="C83" t="n">
+        <v>43</v>
+      </c>
+      <c r="D83" t="n">
+        <v>20</v>
+      </c>
+      <c r="E83" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B84" t="n">
+        <v>23</v>
+      </c>
+      <c r="C84" t="n">
+        <v>17</v>
+      </c>
+      <c r="D84" t="n">
+        <v>17</v>
+      </c>
+      <c r="E84" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B85" t="n">
+        <v>20</v>
+      </c>
+      <c r="C85" t="n">
+        <v>24</v>
+      </c>
+      <c r="D85" t="n">
+        <v>15</v>
+      </c>
+      <c r="E85" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B86" t="n">
+        <v>46</v>
+      </c>
+      <c r="C86" t="n">
+        <v>34</v>
+      </c>
+      <c r="D86" t="n">
+        <v>28</v>
+      </c>
+      <c r="E86" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B87" t="n">
+        <v>30</v>
+      </c>
+      <c r="C87" t="n">
+        <v>55</v>
+      </c>
+      <c r="D87" t="n">
+        <v>23</v>
+      </c>
+      <c r="E87" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B53" t="n">
-        <v>34</v>
-      </c>
-      <c r="C53" t="n">
-        <v>31.66666666666667</v>
-      </c>
-      <c r="D53" t="n">
-        <v>9</v>
-      </c>
-      <c r="E53" t="n">
-        <v>19.33333333333333</v>
+      <c r="B88" t="n">
+        <v>26</v>
+      </c>
+      <c r="C88" t="n">
+        <v>31</v>
+      </c>
+      <c r="D88" t="n">
+        <v>15</v>
+      </c>
+      <c r="E88" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/cheffelo_trends_monthly.xlsx
+++ b/data/cheffelo_trends_monthly.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,106 +417,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Linas_Matkasse_SE</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Godtlevert_NO</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Adams_Matkasse_NO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Retnemt_DK</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>43496</v>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C2" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>43524</v>
       </c>
       <c r="B3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="B4" t="n">
         <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>43585</v>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>43616</v>
       </c>
       <c r="B6" t="n">
@@ -541,283 +529,283 @@
         <v>33</v>
       </c>
       <c r="E6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="B7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>43677</v>
+      </c>
+      <c r="B8" t="n">
         <v>27</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>43677</v>
-      </c>
-      <c r="B8" t="n">
-        <v>25</v>
-      </c>
       <c r="C8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E8" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>43708</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D9" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C10" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>43769</v>
       </c>
       <c r="B11" t="n">
         <v>60</v>
       </c>
       <c r="C11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>43799</v>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" t="n">
         <v>38</v>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E12" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="B13" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C13" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
         <v>32</v>
       </c>
       <c r="E13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>43861</v>
       </c>
       <c r="B14" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E14" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>43890</v>
       </c>
       <c r="B15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E15" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="B16" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16" t="n">
         <v>83</v>
       </c>
       <c r="D16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>43951</v>
       </c>
       <c r="B17" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C17" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>43982</v>
       </c>
       <c r="B18" t="n">
         <v>45</v>
       </c>
       <c r="C18" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
         <v>46</v>
       </c>
       <c r="E18" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="B19" t="n">
         <v>36</v>
       </c>
       <c r="C19" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D19" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>44043</v>
       </c>
       <c r="B20" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C20" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>44074</v>
       </c>
       <c r="B21" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C21" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D21" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="B22" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C22" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D22" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E22" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>44135</v>
       </c>
       <c r="B23" t="n">
@@ -827,133 +815,133 @@
         <v>80</v>
       </c>
       <c r="D23" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>44165</v>
       </c>
       <c r="B24" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C24" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D24" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="B25" t="n">
         <v>54</v>
       </c>
       <c r="C25" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>44227</v>
       </c>
       <c r="B26" t="n">
         <v>100</v>
       </c>
       <c r="C26" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D26" t="n">
         <v>100</v>
       </c>
       <c r="E26" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>44255</v>
       </c>
       <c r="B27" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D27" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E27" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="B28" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C28" t="n">
         <v>79</v>
       </c>
       <c r="D28" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E28" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B29" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C29" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D29" t="n">
         <v>61</v>
       </c>
       <c r="E29" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>44347</v>
       </c>
       <c r="B30" t="n">
         <v>42</v>
       </c>
       <c r="C30" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D30" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E30" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="B31" t="n">
@@ -966,69 +954,69 @@
         <v>32</v>
       </c>
       <c r="E31" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="B32" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C32" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D32" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E32" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="B33" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C33" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D33" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E33" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="B34" t="n">
         <v>48</v>
       </c>
       <c r="C34" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D34" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="B35" t="n">
         <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D35" t="n">
         <v>48</v>
@@ -1038,133 +1026,133 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="B36" t="n">
         <v>37</v>
       </c>
       <c r="C36" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D36" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B37" t="n">
         <v>29</v>
       </c>
       <c r="C37" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D37" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E37" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>44592</v>
       </c>
       <c r="B38" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C38" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D38" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E38" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B39" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C39" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E39" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="B40" t="n">
         <v>42</v>
       </c>
       <c r="C40" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D40" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E40" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>44681</v>
       </c>
       <c r="B41" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C41" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D41" t="n">
         <v>36</v>
       </c>
       <c r="E41" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>44712</v>
       </c>
       <c r="B42" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C42" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D42" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E42" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="B43" t="n">
         <v>25</v>
       </c>
       <c r="C43" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D43" t="n">
         <v>25</v>
@@ -1174,65 +1162,65 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="B44" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C44" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D44" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E44" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="B45" t="n">
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D45" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E45" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B46" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C46" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D46" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E46" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>44865</v>
       </c>
       <c r="B47" t="n">
         <v>38</v>
       </c>
       <c r="C47" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D47" t="n">
         <v>41</v>
@@ -1242,11 +1230,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>44895</v>
       </c>
       <c r="B48" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C48" t="n">
         <v>34</v>
@@ -1255,120 +1243,120 @@
         <v>33</v>
       </c>
       <c r="E48" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="B49" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C49" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D49" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E49" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>44957</v>
       </c>
       <c r="B50" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C50" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D50" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E50" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B51" t="n">
         <v>39</v>
       </c>
       <c r="C51" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D51" t="n">
         <v>45</v>
       </c>
       <c r="E51" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B52" t="n">
+        <v>36</v>
+      </c>
+      <c r="C52" t="n">
+        <v>43</v>
+      </c>
+      <c r="D52" t="n">
+        <v>32</v>
+      </c>
+      <c r="E52" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>45046</v>
+      </c>
+      <c r="B53" t="n">
+        <v>28</v>
+      </c>
+      <c r="C53" t="n">
+        <v>38</v>
+      </c>
+      <c r="D53" t="n">
+        <v>24</v>
+      </c>
+      <c r="E53" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>45016</v>
-      </c>
-      <c r="B52" t="n">
-        <v>35</v>
-      </c>
-      <c r="C52" t="n">
-        <v>35</v>
-      </c>
-      <c r="D52" t="n">
-        <v>30</v>
-      </c>
-      <c r="E52" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>45046</v>
-      </c>
-      <c r="B53" t="n">
-        <v>27</v>
-      </c>
-      <c r="C53" t="n">
-        <v>37</v>
-      </c>
-      <c r="D53" t="n">
-        <v>25</v>
-      </c>
-      <c r="E53" t="n">
-        <v>21</v>
-      </c>
-    </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="B54" t="n">
         <v>22</v>
       </c>
       <c r="C54" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D54" t="n">
         <v>21</v>
       </c>
       <c r="E54" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>45107</v>
+      </c>
+      <c r="B55" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>45107</v>
-      </c>
-      <c r="B55" t="n">
-        <v>17</v>
-      </c>
       <c r="C55" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D55" t="n">
         <v>21</v>
@@ -1378,82 +1366,82 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>45138</v>
       </c>
       <c r="B56" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C56" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D56" t="n">
         <v>20</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>45169</v>
       </c>
       <c r="B57" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C57" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D57" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E57" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="B58" t="n">
+        <v>34</v>
+      </c>
+      <c r="C58" t="n">
+        <v>40</v>
+      </c>
+      <c r="D58" t="n">
         <v>33</v>
       </c>
-      <c r="C58" t="n">
-        <v>38</v>
-      </c>
-      <c r="D58" t="n">
-        <v>34</v>
-      </c>
       <c r="E58" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="B59" t="n">
         <v>32</v>
       </c>
       <c r="C59" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D59" t="n">
         <v>30</v>
       </c>
       <c r="E59" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="B60" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C60" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D60" t="n">
         <v>25</v>
@@ -1463,479 +1451,496 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="B61" t="n">
         <v>22</v>
       </c>
       <c r="C61" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D61" t="n">
         <v>17</v>
       </c>
       <c r="E61" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>45322</v>
+      </c>
+      <c r="B62" t="n">
+        <v>45</v>
+      </c>
+      <c r="C62" t="n">
+        <v>37</v>
+      </c>
+      <c r="D62" t="n">
+        <v>45</v>
+      </c>
+      <c r="E62" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="B63" t="n">
+        <v>29</v>
+      </c>
+      <c r="C63" t="n">
+        <v>42</v>
+      </c>
+      <c r="D63" t="n">
         <v>30</v>
       </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>45322</v>
-      </c>
-      <c r="B62" t="n">
-        <v>44</v>
-      </c>
-      <c r="C62" t="n">
+      <c r="E63" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B64" t="n">
+        <v>24</v>
+      </c>
+      <c r="C64" t="n">
         <v>27</v>
       </c>
-      <c r="D62" t="n">
-        <v>47</v>
-      </c>
-      <c r="E62" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>45351</v>
-      </c>
-      <c r="B63" t="n">
-        <v>31</v>
-      </c>
-      <c r="C63" t="n">
-        <v>41</v>
-      </c>
-      <c r="D63" t="n">
-        <v>31</v>
-      </c>
-      <c r="E63" t="n">
+      <c r="D64" t="n">
+        <v>26</v>
+      </c>
+      <c r="E64" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>45412</v>
+      </c>
+      <c r="B65" t="n">
+        <v>27</v>
+      </c>
+      <c r="C65" t="n">
         <v>24</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>45382</v>
-      </c>
-      <c r="B64" t="n">
-        <v>23</v>
-      </c>
-      <c r="C64" t="n">
-        <v>21</v>
-      </c>
-      <c r="D64" t="n">
-        <v>27</v>
-      </c>
-      <c r="E64" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>45412</v>
-      </c>
-      <c r="B65" t="n">
-        <v>26</v>
-      </c>
-      <c r="C65" t="n">
-        <v>0</v>
       </c>
       <c r="D65" t="n">
         <v>23</v>
       </c>
       <c r="E65" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B66" t="n">
         <v>18</v>
       </c>
       <c r="C66" t="n">
+        <v>18</v>
+      </c>
+      <c r="D66" t="n">
+        <v>19</v>
+      </c>
+      <c r="E66" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>45473</v>
+      </c>
+      <c r="B67" t="n">
         <v>15</v>
       </c>
-      <c r="D66" t="n">
-        <v>17</v>
-      </c>
-      <c r="E66" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>45473</v>
-      </c>
-      <c r="B67" t="n">
-        <v>14</v>
-      </c>
       <c r="C67" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D67" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E67" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>45504</v>
       </c>
       <c r="B68" t="n">
         <v>15</v>
       </c>
       <c r="C68" t="n">
+        <v>28</v>
+      </c>
+      <c r="D68" t="n">
         <v>16</v>
       </c>
-      <c r="D68" t="n">
-        <v>17</v>
-      </c>
       <c r="E68" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>45535</v>
       </c>
       <c r="B69" t="n">
         <v>35</v>
       </c>
       <c r="C69" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D69" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E69" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="B70" t="n">
         <v>29</v>
       </c>
       <c r="C70" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D70" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E70" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>45596</v>
       </c>
       <c r="B71" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C71" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D71" t="n">
         <v>27</v>
       </c>
       <c r="E71" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>45626</v>
       </c>
       <c r="B72" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C72" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D72" t="n">
         <v>20</v>
       </c>
       <c r="E72" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="B73" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C73" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D73" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B74" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C74" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D74" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E74" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B75" t="n">
         <v>28</v>
       </c>
       <c r="C75" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D75" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E75" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="B76" t="n">
         <v>24</v>
       </c>
       <c r="C76" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D76" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E76" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>45777</v>
       </c>
       <c r="B77" t="n">
         <v>16</v>
       </c>
       <c r="C77" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D77" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E77" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>45808</v>
       </c>
       <c r="B78" t="n">
         <v>17</v>
       </c>
       <c r="C78" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D78" t="n">
         <v>15</v>
       </c>
       <c r="E78" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B79" t="n">
         <v>14</v>
       </c>
       <c r="C79" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E79" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="B80" t="n">
         <v>14</v>
       </c>
       <c r="C80" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D80" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>45900</v>
       </c>
       <c r="B81" t="n">
         <v>39</v>
       </c>
       <c r="C81" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D81" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E81" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="B82" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C82" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D82" t="n">
         <v>34</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B83" t="n">
         <v>27</v>
       </c>
       <c r="C83" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E83" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>45991</v>
       </c>
       <c r="B84" t="n">
         <v>23</v>
       </c>
       <c r="C84" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D84" t="n">
         <v>17</v>
       </c>
       <c r="E84" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="B85" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C85" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E85" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B86" t="n">
+        <v>47</v>
+      </c>
+      <c r="C86" t="n">
         <v>46</v>
       </c>
-      <c r="C86" t="n">
+      <c r="D86" t="n">
+        <v>27</v>
+      </c>
+      <c r="E86" t="n">
         <v>34</v>
       </c>
-      <c r="D86" t="n">
-        <v>28</v>
-      </c>
-      <c r="E86" t="n">
-        <v>33</v>
-      </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>46081</v>
       </c>
       <c r="B87" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C87" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D87" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E87" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B88" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C88" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E88" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B89" t="n">
+        <v>13</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/cheffelo_trends_monthly.xlsx
+++ b/data/cheffelo_trends_monthly.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,453 +429,453 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Linas_Matkasse_SE</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Godtlevert_NO</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Adams_Matkasse_NO</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Retnemt_DK</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C2" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B3" t="n">
         <v>53</v>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D3" t="n">
         <v>50</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B4" t="n">
         <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B5" t="n">
+        <v>35</v>
+      </c>
+      <c r="C5" t="n">
         <v>36</v>
-      </c>
-      <c r="C5" t="n">
-        <v>58</v>
       </c>
       <c r="D5" t="n">
         <v>44</v>
       </c>
       <c r="E5" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>43616</v>
+      </c>
+      <c r="B6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D6" t="n">
+        <v>32</v>
+      </c>
+      <c r="E6" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>43616</v>
-      </c>
-      <c r="B6" t="n">
-        <v>36</v>
-      </c>
-      <c r="C6" t="n">
-        <v>34</v>
-      </c>
-      <c r="D6" t="n">
-        <v>33</v>
-      </c>
-      <c r="E6" t="n">
-        <v>27</v>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B7" t="n">
         <v>33</v>
       </c>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E7" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E8" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B9" t="n">
         <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B10" t="n">
         <v>73</v>
       </c>
       <c r="C10" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B11" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B12" t="n">
         <v>50</v>
       </c>
       <c r="C12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E12" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B13" t="n">
         <v>46</v>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B14" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C14" t="n">
+        <v>71</v>
+      </c>
+      <c r="D14" t="n">
         <v>74</v>
-      </c>
-      <c r="D14" t="n">
-        <v>73</v>
       </c>
       <c r="E14" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B15" t="n">
         <v>55</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B17" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D17" t="n">
         <v>60</v>
       </c>
       <c r="E17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B18" t="n">
         <v>45</v>
       </c>
       <c r="C18" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E18" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B19" t="n">
         <v>36</v>
       </c>
       <c r="C19" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B20" t="n">
         <v>32</v>
       </c>
       <c r="C20" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D20" t="n">
         <v>28</v>
       </c>
       <c r="E20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B21" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C21" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D21" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E21" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B22" t="n">
         <v>78</v>
       </c>
       <c r="C22" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D22" t="n">
         <v>85</v>
       </c>
       <c r="E22" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B23" t="n">
         <v>57</v>
       </c>
       <c r="C23" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D23" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E23" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B24" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C24" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D24" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E24" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B25" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C25" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D25" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E25" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B26" t="n">
         <v>100</v>
       </c>
       <c r="C26" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D26" t="n">
         <v>100</v>
@@ -873,181 +885,181 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B27" t="n">
         <v>77</v>
       </c>
       <c r="C27" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D27" t="n">
         <v>75</v>
       </c>
       <c r="E27" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B28" t="n">
         <v>70</v>
       </c>
       <c r="C28" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D28" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E28" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B29" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C29" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D29" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E29" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B30" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C30" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D30" t="n">
         <v>45</v>
       </c>
       <c r="E30" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B31" t="n">
         <v>27</v>
       </c>
       <c r="C31" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D31" t="n">
         <v>32</v>
       </c>
       <c r="E31" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C32" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D32" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E32" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B33" t="n">
         <v>48</v>
       </c>
       <c r="C33" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D33" t="n">
         <v>74</v>
       </c>
       <c r="E33" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B34" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C34" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E34" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B35" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C35" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D35" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E35" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B36" t="n">
         <v>37</v>
       </c>
       <c r="C36" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D36" t="n">
         <v>37</v>
       </c>
       <c r="E36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B37" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C37" t="n">
         <v>47</v>
@@ -1056,113 +1068,113 @@
         <v>33</v>
       </c>
       <c r="E37" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B38" t="n">
         <v>62</v>
       </c>
       <c r="C38" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D38" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E38" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B39" t="n">
         <v>41</v>
       </c>
       <c r="C39" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D39" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E39" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B40" t="n">
         <v>42</v>
       </c>
       <c r="C40" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D40" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E40" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B41" t="n">
         <v>35</v>
       </c>
       <c r="C41" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D41" t="n">
         <v>36</v>
       </c>
       <c r="E41" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B42" t="n">
         <v>34</v>
       </c>
       <c r="C42" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D42" t="n">
         <v>32</v>
       </c>
       <c r="E42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B43" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C43" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D43" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E43" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B44" t="n">
@@ -1175,11 +1187,11 @@
         <v>22</v>
       </c>
       <c r="E44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B45" t="n">
@@ -1189,259 +1201,259 @@
         <v>50</v>
       </c>
       <c r="D45" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E45" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B46" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C46" t="n">
+        <v>52</v>
+      </c>
+      <c r="D46" t="n">
         <v>47</v>
       </c>
-      <c r="D46" t="n">
-        <v>48</v>
-      </c>
       <c r="E46" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B47" t="n">
         <v>38</v>
       </c>
       <c r="C47" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D47" t="n">
         <v>41</v>
       </c>
       <c r="E47" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B48" t="n">
         <v>32</v>
       </c>
       <c r="C48" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D48" t="n">
         <v>33</v>
       </c>
       <c r="E48" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B49" t="n">
         <v>29</v>
       </c>
       <c r="C49" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D49" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B50" t="n">
         <v>73</v>
       </c>
       <c r="C50" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E50" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B51" t="n">
         <v>39</v>
       </c>
       <c r="C51" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D51" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E51" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B52" t="n">
         <v>36</v>
       </c>
       <c r="C52" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D52" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E52" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B53" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C53" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D53" t="n">
         <v>24</v>
       </c>
       <c r="E53" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B54" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C54" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D54" t="n">
         <v>21</v>
       </c>
       <c r="E54" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B55" t="n">
         <v>18</v>
       </c>
       <c r="C55" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D55" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E55" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B56" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C56" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B57" t="n">
         <v>44</v>
       </c>
       <c r="C57" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D57" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E57" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B58" t="n">
         <v>34</v>
       </c>
       <c r="C58" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D58" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E58" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B59" t="n">
         <v>32</v>
       </c>
       <c r="C59" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D59" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E59" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B60" t="n">
         <v>27</v>
       </c>
       <c r="C60" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D60" t="n">
         <v>25</v>
@@ -1451,14 +1463,14 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B61" t="n">
         <v>22</v>
       </c>
       <c r="C61" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D61" t="n">
         <v>17</v>
@@ -1468,65 +1480,65 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B62" t="n">
         <v>45</v>
       </c>
       <c r="C62" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D62" t="n">
+        <v>44</v>
+      </c>
+      <c r="E62" t="n">
         <v>45</v>
       </c>
-      <c r="E62" t="n">
-        <v>46</v>
-      </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B63" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C63" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D63" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E63" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B64" t="n">
         <v>23</v>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>45382</v>
-      </c>
-      <c r="B64" t="n">
-        <v>24</v>
-      </c>
       <c r="C64" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D64" t="n">
         <v>26</v>
       </c>
       <c r="E64" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B65" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C65" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D65" t="n">
         <v>23</v>
@@ -1536,411 +1548,496 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B66" t="n">
         <v>18</v>
       </c>
       <c r="C66" t="n">
+        <v>17</v>
+      </c>
+      <c r="D66" t="n">
         <v>18</v>
       </c>
-      <c r="D66" t="n">
-        <v>19</v>
-      </c>
       <c r="E66" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B67" t="n">
         <v>15</v>
       </c>
       <c r="C67" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D67" t="n">
         <v>12</v>
       </c>
       <c r="E67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B68" t="n">
         <v>15</v>
       </c>
       <c r="C68" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D68" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E68" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B69" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C69" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D69" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E69" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B70" t="n">
         <v>29</v>
       </c>
       <c r="C70" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D70" t="n">
         <v>28</v>
       </c>
       <c r="E70" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B71" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C71" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D71" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E71" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B72" t="n">
         <v>22</v>
       </c>
       <c r="C72" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D72" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E72" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B73" t="n">
         <v>17</v>
       </c>
       <c r="C73" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D73" t="n">
         <v>17</v>
       </c>
       <c r="E73" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B74" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C74" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D74" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E74" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B75" t="n">
+        <v>29</v>
+      </c>
+      <c r="C75" t="n">
+        <v>61</v>
+      </c>
+      <c r="D75" t="n">
         <v>28</v>
-      </c>
-      <c r="C75" t="n">
-        <v>72</v>
-      </c>
-      <c r="D75" t="n">
-        <v>27</v>
       </c>
       <c r="E75" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B76" t="n">
         <v>24</v>
       </c>
       <c r="C76" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D76" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E76" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B77" t="n">
         <v>16</v>
       </c>
       <c r="C77" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D77" t="n">
         <v>21</v>
       </c>
       <c r="E77" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B78" t="n">
         <v>17</v>
       </c>
       <c r="C78" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D78" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E78" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B79" t="n">
         <v>14</v>
       </c>
       <c r="C79" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D79" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B80" t="n">
         <v>14</v>
       </c>
       <c r="C80" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B81" t="n">
         <v>39</v>
       </c>
       <c r="C81" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E81" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B82" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C82" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D82" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E82" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B83" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C83" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E83" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B84" t="n">
         <v>23</v>
       </c>
       <c r="C84" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
         <v>17</v>
       </c>
       <c r="E84" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B85" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E85" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B86" t="n">
         <v>47</v>
       </c>
       <c r="C86" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D86" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E86" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B87" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C87" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D87" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E87" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B88" t="n">
         <v>25</v>
       </c>
       <c r="C88" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D88" t="n">
+        <v>12</v>
+      </c>
+      <c r="E88" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B89" t="n">
+        <v>21</v>
+      </c>
+      <c r="C89" t="n">
+        <v>32</v>
+      </c>
+      <c r="D89" t="n">
+        <v>9</v>
+      </c>
+      <c r="E89" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B90" t="n">
+        <v>17</v>
+      </c>
+      <c r="C90" t="n">
+        <v>28</v>
+      </c>
+      <c r="D90" t="n">
+        <v>7</v>
+      </c>
+      <c r="E90" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B91" t="n">
+        <v>15</v>
+      </c>
+      <c r="C91" t="n">
+        <v>24</v>
+      </c>
+      <c r="D91" t="n">
+        <v>5</v>
+      </c>
+      <c r="E91" t="n">
         <v>10</v>
       </c>
-      <c r="E88" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="B89" t="n">
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B92" t="n">
+        <v>14</v>
+      </c>
+      <c r="C92" t="n">
+        <v>28</v>
+      </c>
+      <c r="D92" t="n">
+        <v>6</v>
+      </c>
+      <c r="E92" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B93" t="n">
+        <v>35</v>
+      </c>
+      <c r="C93" t="n">
+        <v>64</v>
+      </c>
+      <c r="D93" t="n">
         <v>13</v>
       </c>
-      <c r="C89" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0</v>
+      <c r="E93" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B94" t="n">
+        <v>31</v>
+      </c>
+      <c r="C94" t="n">
+        <v>64</v>
+      </c>
+      <c r="D94" t="n">
+        <v>12</v>
+      </c>
+      <c r="E94" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
